--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487516_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487516_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6679</v>
+        <v>5.1654</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2282</v>
+        <v>5.5119</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5603</v>
+        <v>-0.3465</v>
       </c>
       <c r="G2" t="n">
         <v>2.9353</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8536</v>
+        <v>0.3511</v>
       </c>
       <c r="T2" t="n">
-        <v>1.268</v>
+        <v>0.5517</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4144</v>
+        <v>-0.2005</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2754</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.819</v>
+        <v>2.3562</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1054</v>
+        <v>3.6961</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2864</v>
+        <v>-1.3398</v>
       </c>
       <c r="G3" t="n">
         <v>1.7269</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0173</v>
+        <v>-0.4455</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4911</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4738</v>
+        <v>-0.5273</v>
       </c>
       <c r="V3" t="n">
         <v>-0.8837</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3937</v>
+        <v>2.037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7168</v>
+        <v>1.1554</v>
       </c>
       <c r="G4" t="n">
         <v>2.1489</v>
@@ -766,13 +766,13 @@
         <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5938</v>
+        <v>0.2372</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3341</v>
+        <v>-0.1294</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.3666</v>
       </c>
       <c r="V4" t="n">
         <v>0.8260999999999999</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8983</v>
+        <v>1.1832</v>
       </c>
       <c r="E5" t="n">
-        <v>0.648</v>
+        <v>0.8526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2504</v>
+        <v>0.3305</v>
       </c>
       <c r="G5" t="n">
         <v>0.4148</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1247</v>
+        <v>0.1601</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2376</v>
+        <v>-0.0329</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1129</v>
+        <v>0.1931</v>
       </c>
       <c r="V5" t="n">
         <v>0.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4872</v>
+        <v>0.9546</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6598</v>
+        <v>2.9668</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1726</v>
+        <v>-2.0122</v>
       </c>
       <c r="G6" t="n">
         <v>0.8183</v>
@@ -922,13 +922,13 @@
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7423</v>
+        <v>-0.275</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1559</v>
+        <v>0.1511</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5865</v>
+        <v>-0.4261</v>
       </c>
       <c r="V6" t="n">
         <v>0.9988</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2425</v>
+        <v>0.7855</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9119</v>
+        <v>2.3212</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6694</v>
+        <v>-1.5358</v>
       </c>
       <c r="G7" t="n">
         <v>2.7635</v>
@@ -1000,13 +1000,13 @@
         <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5578</v>
+        <v>-0.0149</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2441</v>
+        <v>0.1653</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3138</v>
+        <v>-0.1801</v>
       </c>
       <c r="V7" t="n">
         <v>-1.7673</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3445</v>
+        <v>-0.4201</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4002</v>
+        <v>0.2979</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7447</v>
+        <v>-0.718</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5139</v>
@@ -1078,13 +1078,13 @@
         <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1427</v>
+        <v>-0.2183</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0306</v>
+        <v>-0.1329</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1122</v>
+        <v>-0.0854</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2754</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6355</v>
+        <v>-1.7974</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8864</v>
+        <v>0.2077</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7492</v>
+        <v>-2.0051</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6278</v>
+        <v>-0.6141</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.1661</v>
+        <v>0.6091</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7938</v>
+        <v>-1.2232</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1621</v>
+        <v>1.4816</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9443</v>
+        <v>2.7152</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1064</v>
+        <v>-1.2336</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5344</v>
+        <v>-2.0957</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2218</v>
+        <v>-2.1061</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6874</v>
+        <v>0.0104</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1838</v>
+        <v>-0.4748</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09</v>
+        <v>-0.2947</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1801</v>
       </c>
       <c r="V9" t="n">
         <v>-1.492</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1358</v>
+        <v>-1.8715</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003</v>
+        <v>-0.9887</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1388</v>
+        <v>-0.8828</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6141</v>
+        <v>0.6278</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6091</v>
+        <v>-2.1661</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2232</v>
+        <v>2.7938</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4816</v>
+        <v>1.1621</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7152</v>
+        <v>-0.9443</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2336</v>
+        <v>2.1064</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0957</v>
+        <v>-0.5344</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.1061</v>
+        <v>-1.2218</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0104</v>
+        <v>0.6874</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7834</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8131</v>
+        <v>-0.4198</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4993</v>
+        <v>-0.1923</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3138</v>
+        <v>-0.2275</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.392800000000001</v>
+        <v>8.392899999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>15.747</v>
+        <v>15.7471</v>
       </c>
       <c r="F11" t="n">
-        <v>-7.354200000000001</v>
+        <v>-7.3543</v>
       </c>
       <c r="G11" t="n">
         <v>10.3075</v>
@@ -1312,13 +1312,13 @@
         <v>14.6885</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0997</v>
+        <v>-1.0999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1675000000000001</v>
+        <v>0.1676</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2675</v>
+        <v>-1.2673</v>
       </c>
       <c r="V11" t="n">
         <v>-3.7526</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>L. MC-CARTHY SANTOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.868</v>
+        <v>1.9064</v>
       </c>
       <c r="E12" t="n">
-        <v>5.3753</v>
+        <v>3.023</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5073</v>
+        <v>-1.1166</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.659</v>
+        <v>0.675</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9572000000000001</v>
+        <v>3.6245</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6162</v>
+        <v>-2.9496</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6992</v>
+        <v>5.1686</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9717</v>
+        <v>5.0473</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7275</v>
+        <v>0.1212</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.3582</v>
+        <v>-4.4936</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0145</v>
+        <v>-1.4228</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.3437</v>
+        <v>-3.0708</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9792</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R12" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4624</v>
+        <v>0.3074</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9617</v>
+        <v>-0.0535</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5007</v>
+        <v>0.361</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0438</v>
+        <v>2.4908</v>
       </c>
       <c r="W12" t="n">
-        <v>1.6521</v>
+        <v>1.8249</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6083</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. MC-CARTHY SANTOS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8701</v>
+        <v>0.574</v>
       </c>
       <c r="E13" t="n">
-        <v>2.102</v>
+        <v>2.5699</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2319</v>
+        <v>-1.9959</v>
       </c>
       <c r="G13" t="n">
-        <v>0.675</v>
+        <v>-0.9566</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6245</v>
+        <v>3.4093</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9496</v>
+        <v>-4.3659</v>
       </c>
       <c r="J13" t="n">
-        <v>5.1686</v>
+        <v>2.86</v>
       </c>
       <c r="K13" t="n">
-        <v>5.0473</v>
+        <v>4.5592</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1212</v>
+        <v>-1.6993</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.4936</v>
+        <v>-3.8166</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4228</v>
+        <v>-1.1499</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.0708</v>
+        <v>-2.6667</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R13" t="n">
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7289</v>
+        <v>0.2553</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9745</v>
+        <v>0.1764</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2457</v>
+        <v>0.0788</v>
       </c>
       <c r="V13" t="n">
-        <v>2.4908</v>
+        <v>0.8837</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8249</v>
+        <v>1.492</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6659</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.3013</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0267</v>
+        <v>0.2314</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5504</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3207</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9081</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4576</v>
+        <v>-0.2529</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4506</v>
+        <v>0.1698</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6659</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6724</v>
+        <v>0.2959</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1605</v>
+        <v>2.7146</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.8329</v>
+        <v>-2.4187</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9566</v>
+        <v>-1.659</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4093</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.3659</v>
+        <v>-2.6162</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>2.6992</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5592</v>
+        <v>1.9717</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.6993</v>
+        <v>0.7275</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.8166</v>
+        <v>-4.3582</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1499</v>
+        <v>-1.0145</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.6667</v>
+        <v>-3.3437</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3917</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3502</v>
+        <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9911</v>
+        <v>1.8903</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2329</v>
+        <v>1.3009</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7582</v>
+        <v>0.5893</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8837</v>
+        <v>1.0438</v>
       </c>
       <c r="W15" t="n">
-        <v>1.492</v>
+        <v>1.6521</v>
       </c>
       <c r="X15" t="n">
         <v>-0.6083</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. JIMENEZ EL MERZOUG</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.1038</v>
+        <v>-2.8428</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.897</v>
+        <v>1.1138</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.2068</v>
+        <v>-3.9566</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.9527</v>
+        <v>-3.8613</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3161</v>
+        <v>-0.0775</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.2688</v>
+        <v>-3.7838</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4639</v>
+        <v>0.9729</v>
       </c>
       <c r="K16" t="n">
-        <v>1.788</v>
+        <v>1.6859</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3241</v>
+        <v>-0.713</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4166</v>
+        <v>-4.8342</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4718</v>
+        <v>-1.7634</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.9447</v>
+        <v>-3.0708</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.546</v>
+        <v>1.3709</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3709</v>
+        <v>2.3502</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9029</v>
+        <v>-0.077</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0641</v>
+        <v>-0.0965</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8388</v>
+        <v>0.0194</v>
       </c>
       <c r="V16" t="n">
-        <v>1.492</v>
+        <v>-0.2754</v>
       </c>
       <c r="W16" t="n">
-        <v>1.492</v>
+        <v>1.2166</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.6828</v>
+        <v>-3.0836</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7083</v>
+        <v>-0.299</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9745</v>
+        <v>-2.7846</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2321</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2549</v>
+        <v>0.3444</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1782</v>
+        <v>0.2311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0767</v>
+        <v>0.1132</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2166</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>I. JIMENEZ EL MERZOUG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.1482</v>
+        <v>-3.4974</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2951</v>
+        <v>-1.9993</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.4433</v>
+        <v>-1.4981</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8613</v>
+        <v>-2.9527</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0775</v>
+        <v>1.3161</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.7838</v>
+        <v>-4.2688</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9729</v>
+        <v>0.4639</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6859</v>
+        <v>1.788</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.713</v>
+        <v>-1.3241</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.8342</v>
+        <v>-3.4166</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7634</v>
+        <v>-0.4718</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.0708</v>
+        <v>-2.9447</v>
       </c>
       <c r="P18" t="n">
+        <v>-2.546</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-3.917</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.3709</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.9792</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.3502</v>
-      </c>
       <c r="S18" t="n">
-        <v>-1.3825</v>
+        <v>0.5093</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9151</v>
+        <v>-0.0382</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4673</v>
+        <v>0.5476</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2754</v>
+        <v>1.492</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2166</v>
+        <v>1.492</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-8.392800000000001</v>
+        <v>-6.3462</v>
       </c>
       <c r="E19" t="n">
-        <v>7.354299999999999</v>
+        <v>7.3544</v>
       </c>
       <c r="F19" t="n">
-        <v>-15.7471</v>
+        <v>-13.7005</v>
       </c>
       <c r="G19" t="n">
         <v>-10.3074</v>
@@ -1921,7 +1921,7 @@
         <v>-23.4629</v>
       </c>
       <c r="N19" t="n">
-        <v>-6.088</v>
+        <v>-6.088000000000001</v>
       </c>
       <c r="O19" t="n">
         <v>-17.3748</v>
@@ -1936,13 +1936,13 @@
         <v>11.7509</v>
       </c>
       <c r="S19" t="n">
-        <v>1.099799999999999</v>
+        <v>3.1466</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2675</v>
+        <v>1.2673</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1675999999999999</v>
+        <v>1.8791</v>
       </c>
       <c r="V19" t="n">
         <v>3.752400000000001</v>
